--- a/Balance_Semanal.xlsx
+++ b/Balance_Semanal.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="112">
   <si>
     <t xml:space="preserve">AGRO PACAYALES · PLANTA CAMOTE 2026  |  Balance Diario de Selección &amp; Despacho SUPESA</t>
   </si>
@@ -2439,10 +2439,10 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="21" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C16" s="13" t="n">
         <v>22</v>
@@ -2541,18 +2541,11 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="21" t="s">
-        <v>61</v>
-      </c>
-      <c r="B17" s="0" t="s">
-        <v>42</v>
-      </c>
-      <c r="C17" s="13" t="n">
-        <v>70</v>
-      </c>
+      <c r="A17" s="21"/>
+      <c r="C17" s="13"/>
       <c r="D17" s="13" t="n">
         <f aca="false">C17*95</f>
-        <v>6650</v>
+        <v>0</v>
       </c>
       <c r="E17" s="14"/>
       <c r="F17" s="14"/>
@@ -4016,7 +4009,7 @@
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="26" t="str">
         <f aca="false">IFERROR(INDEX(FIFO_helper!$AP$1:$AP$241,MATCH(29,FIFO_helper!$AW$1:$AW$241,0)),"")</f>
-        <v>20/07</v>
+        <v>21/07</v>
       </c>
       <c r="B31" s="26" t="str">
         <f aca="false">IFERROR(INDEX(FIFO_helper!$AQ$1:$AQ$241,MATCH(29,FIFO_helper!$AW$1:$AW$241,0)),"")</f>
@@ -4043,7 +4036,7 @@
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="26" t="str">
         <f aca="false">IFERROR(INDEX(FIFO_helper!$AP$1:$AP$241,MATCH(30,FIFO_helper!$AW$1:$AW$241,0)),"")</f>
-        <v>20/07</v>
+        <v>21/07</v>
       </c>
       <c r="B32" s="26" t="str">
         <f aca="false">IFERROR(INDEX(FIFO_helper!$AQ$1:$AQ$241,MATCH(30,FIFO_helper!$AW$1:$AW$241,0)),"")</f>
@@ -4070,7 +4063,7 @@
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="26" t="str">
         <f aca="false">IFERROR(INDEX(FIFO_helper!$AP$1:$AP$241,MATCH(31,FIFO_helper!$AW$1:$AW$241,0)),"")</f>
-        <v>20/07</v>
+        <v>21/07</v>
       </c>
       <c r="B33" s="26" t="str">
         <f aca="false">IFERROR(INDEX(FIFO_helper!$AQ$1:$AQ$241,MATCH(31,FIFO_helper!$AW$1:$AW$241,0)),"")</f>
@@ -4097,28 +4090,28 @@
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="26" t="str">
         <f aca="false">IFERROR(INDEX(FIFO_helper!$AP$1:$AP$241,MATCH(32,FIFO_helper!$AW$1:$AW$241,0)),"")</f>
-        <v>21/07</v>
+        <v/>
       </c>
       <c r="B34" s="26" t="str">
         <f aca="false">IFERROR(INDEX(FIFO_helper!$AQ$1:$AQ$241,MATCH(32,FIFO_helper!$AW$1:$AW$241,0)),"")</f>
-        <v>(queda en planta)</v>
+        <v/>
       </c>
       <c r="C34" s="26"/>
       <c r="D34" s="26" t="str">
         <f aca="false">IFERROR(INDEX(FIFO_helper!$AR$1:$AR$241,MATCH(32,FIFO_helper!$AW$1:$AW$241,0)),"")</f>
-        <v>PRIMERA</v>
+        <v/>
       </c>
       <c r="E34" s="26" t="str">
         <f aca="false">IFERROR(INDEX(FIFO_helper!$AS$1:$AS$241,MATCH(32,FIFO_helper!$AW$1:$AW$241,0)),"")</f>
         <v/>
       </c>
-      <c r="F34" s="26" t="n">
+      <c r="F34" s="26" t="str">
         <f aca="false">IFERROR(INDEX(FIFO_helper!$AT$1:$AT$241,MATCH(32,FIFO_helper!$AW$1:$AW$241,0)),"")</f>
-        <v>6650</v>
+        <v/>
       </c>
       <c r="G34" s="26" t="str">
         <f aca="false">IFERROR(INDEX(FIFO_helper!$AU$1:$AU$241,MATCH(32,FIFO_helper!$AW$1:$AW$241,0)),"")</f>
-        <v>kg</v>
+        <v/>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7765,7 +7758,7 @@
       </c>
       <c r="C13" s="0" t="str">
         <f aca="false">IF(B13=5,"sem. ant.",INDEX('Balance PLANTA'!$A:$A,B13))</f>
-        <v>20/07</v>
+        <v>21/07</v>
       </c>
       <c r="D13" s="0" t="n">
         <f aca="false">IF(B13=5,INDEX('Balance PLANTA'!$R:$R,B13)*15+INDEX('Balance PLANTA'!$S:$S,B13)*18+INDEX('Balance PLANTA'!$T:$T,B13)*17+INDEX('Balance PLANTA'!$U:$U,B13)*17,IFERROR(INDEX('Balance PLANTA'!$C:$C,B13)*95,0))</f>
@@ -7912,13 +7905,13 @@
         <f aca="false">A14+4</f>
         <v>17</v>
       </c>
-      <c r="C14" s="0" t="str">
+      <c r="C14" s="0" t="n">
         <f aca="false">IF(B14=5,"sem. ant.",INDEX('Balance PLANTA'!$A:$A,B14))</f>
-        <v>21/07</v>
+        <v>0</v>
       </c>
       <c r="D14" s="0" t="n">
         <f aca="false">IF(B14=5,INDEX('Balance PLANTA'!$R:$R,B14)*15+INDEX('Balance PLANTA'!$S:$S,B14)*18+INDEX('Balance PLANTA'!$T:$T,B14)*17+INDEX('Balance PLANTA'!$U:$U,B14)*17,IFERROR(INDEX('Balance PLANTA'!$C:$C,B14)*95,0))</f>
-        <v>6650</v>
+        <v>0</v>
       </c>
       <c r="E14" s="0" t="n">
         <f aca="false">IF(B14=5,0,IFERROR(INDEX('Balance PLANTA'!$W:$W,B14),0))</f>
@@ -7930,11 +7923,11 @@
       </c>
       <c r="G14" s="0" t="n">
         <f aca="false">D14-F14</f>
-        <v>6650</v>
+        <v>0</v>
       </c>
       <c r="H14" s="0" t="n">
         <f aca="false">H13+G14</f>
-        <v>37004</v>
+        <v>30354</v>
       </c>
       <c r="I14" s="0" t="n">
         <f aca="false">IFERROR(INDEX('Balance PLANTA'!$L:$L,B14)*15+INDEX('Balance PLANTA'!$M:$M,B14)*18+INDEX('Balance PLANTA'!$N:$N,B14)*17+INDEX('Balance PLANTA'!$O:$O,B14)*17,0)</f>
@@ -8018,7 +8011,7 @@
       </c>
       <c r="AN14" s="0" t="n">
         <f aca="false">MAX(0,H14-MAX(H13,$N$1))</f>
-        <v>6650</v>
+        <v>0</v>
       </c>
       <c r="AP14" s="0" t="str">
         <f aca="false">IF($R$4&lt;=0,"",FIFO_helper!$C$4)</f>
@@ -8083,7 +8076,7 @@
       </c>
       <c r="H15" s="0" t="n">
         <f aca="false">H14+G15</f>
-        <v>37004</v>
+        <v>30354</v>
       </c>
       <c r="I15" s="0" t="n">
         <f aca="false">IFERROR(INDEX('Balance PLANTA'!$L:$L,B15)*15+INDEX('Balance PLANTA'!$M:$M,B15)*18+INDEX('Balance PLANTA'!$N:$N,B15)*17+INDEX('Balance PLANTA'!$O:$O,B15)*17,0)</f>
@@ -8232,7 +8225,7 @@
       </c>
       <c r="H16" s="0" t="n">
         <f aca="false">H15+G16</f>
-        <v>37004</v>
+        <v>30354</v>
       </c>
       <c r="I16" s="0" t="n">
         <f aca="false">IFERROR(INDEX('Balance PLANTA'!$L:$L,B16)*15+INDEX('Balance PLANTA'!$M:$M,B16)*18+INDEX('Balance PLANTA'!$N:$N,B16)*17+INDEX('Balance PLANTA'!$O:$O,B16)*17,0)</f>
@@ -8381,7 +8374,7 @@
       </c>
       <c r="H17" s="0" t="n">
         <f aca="false">H16+G17</f>
-        <v>37004</v>
+        <v>30354</v>
       </c>
       <c r="I17" s="0" t="n">
         <f aca="false">IFERROR(INDEX('Balance PLANTA'!$L:$L,B17)*15+INDEX('Balance PLANTA'!$M:$M,B17)*18+INDEX('Balance PLANTA'!$N:$N,B17)*17+INDEX('Balance PLANTA'!$O:$O,B17)*17,0)</f>
@@ -8530,7 +8523,7 @@
       </c>
       <c r="H18" s="0" t="n">
         <f aca="false">H17+G18</f>
-        <v>37004</v>
+        <v>30354</v>
       </c>
       <c r="I18" s="0" t="n">
         <f aca="false">IFERROR(INDEX('Balance PLANTA'!$L:$L,B18)*15+INDEX('Balance PLANTA'!$M:$M,B18)*18+INDEX('Balance PLANTA'!$N:$N,B18)*17+INDEX('Balance PLANTA'!$O:$O,B18)*17,0)</f>
@@ -8679,7 +8672,7 @@
       </c>
       <c r="H19" s="0" t="n">
         <f aca="false">H18+G19</f>
-        <v>37004</v>
+        <v>30354</v>
       </c>
       <c r="I19" s="0" t="n">
         <f aca="false">IFERROR(INDEX('Balance PLANTA'!$L:$L,B19)*15+INDEX('Balance PLANTA'!$M:$M,B19)*18+INDEX('Balance PLANTA'!$N:$N,B19)*17+INDEX('Balance PLANTA'!$O:$O,B19)*17,0)</f>
@@ -8828,7 +8821,7 @@
       </c>
       <c r="H20" s="0" t="n">
         <f aca="false">H19+G20</f>
-        <v>37004</v>
+        <v>30354</v>
       </c>
       <c r="I20" s="0" t="n">
         <f aca="false">IFERROR(INDEX('Balance PLANTA'!$L:$L,B20)*15+INDEX('Balance PLANTA'!$M:$M,B20)*18+INDEX('Balance PLANTA'!$N:$N,B20)*17+INDEX('Balance PLANTA'!$O:$O,B20)*17,0)</f>
@@ -8977,7 +8970,7 @@
       </c>
       <c r="H21" s="0" t="n">
         <f aca="false">H20+G21</f>
-        <v>37004</v>
+        <v>30354</v>
       </c>
       <c r="I21" s="0" t="n">
         <f aca="false">IFERROR(INDEX('Balance PLANTA'!$L:$L,B21)*15+INDEX('Balance PLANTA'!$M:$M,B21)*18+INDEX('Balance PLANTA'!$N:$N,B21)*17+INDEX('Balance PLANTA'!$O:$O,B21)*17,0)</f>
@@ -9126,7 +9119,7 @@
       </c>
       <c r="H22" s="0" t="n">
         <f aca="false">H21+G22</f>
-        <v>37004</v>
+        <v>30354</v>
       </c>
       <c r="I22" s="0" t="n">
         <f aca="false">IFERROR(INDEX('Balance PLANTA'!$L:$L,B22)*15+INDEX('Balance PLANTA'!$M:$M,B22)*18+INDEX('Balance PLANTA'!$N:$N,B22)*17+INDEX('Balance PLANTA'!$O:$O,B22)*17,0)</f>
@@ -9275,7 +9268,7 @@
       </c>
       <c r="H23" s="0" t="n">
         <f aca="false">H22+G23</f>
-        <v>37004</v>
+        <v>30354</v>
       </c>
       <c r="I23" s="0" t="n">
         <f aca="false">IFERROR(INDEX('Balance PLANTA'!$L:$L,B23)*15+INDEX('Balance PLANTA'!$M:$M,B23)*18+INDEX('Balance PLANTA'!$N:$N,B23)*17+INDEX('Balance PLANTA'!$O:$O,B23)*17,0)</f>
@@ -9424,7 +9417,7 @@
       </c>
       <c r="H24" s="0" t="n">
         <f aca="false">H23+G24</f>
-        <v>37004</v>
+        <v>30354</v>
       </c>
       <c r="I24" s="0" t="n">
         <f aca="false">IFERROR(INDEX('Balance PLANTA'!$L:$L,B24)*15+INDEX('Balance PLANTA'!$M:$M,B24)*18+INDEX('Balance PLANTA'!$N:$N,B24)*17+INDEX('Balance PLANTA'!$O:$O,B24)*17,0)</f>
@@ -9573,7 +9566,7 @@
       </c>
       <c r="H25" s="0" t="n">
         <f aca="false">H24+G25</f>
-        <v>37004</v>
+        <v>30354</v>
       </c>
       <c r="I25" s="0" t="n">
         <f aca="false">IFERROR(INDEX('Balance PLANTA'!$L:$L,B25)*15+INDEX('Balance PLANTA'!$M:$M,B25)*18+INDEX('Balance PLANTA'!$N:$N,B25)*17+INDEX('Balance PLANTA'!$O:$O,B25)*17,0)</f>
@@ -9722,7 +9715,7 @@
       </c>
       <c r="H26" s="0" t="n">
         <f aca="false">H25+G26</f>
-        <v>37004</v>
+        <v>30354</v>
       </c>
       <c r="I26" s="0" t="n">
         <f aca="false">IFERROR(INDEX('Balance PLANTA'!$L:$L,B26)*15+INDEX('Balance PLANTA'!$M:$M,B26)*18+INDEX('Balance PLANTA'!$N:$N,B26)*17+INDEX('Balance PLANTA'!$O:$O,B26)*17,0)</f>
@@ -9871,7 +9864,7 @@
       </c>
       <c r="H27" s="0" t="n">
         <f aca="false">H26+G27</f>
-        <v>37004</v>
+        <v>30354</v>
       </c>
       <c r="I27" s="0" t="n">
         <f aca="false">IFERROR(INDEX('Balance PLANTA'!$L:$L,B27)*15+INDEX('Balance PLANTA'!$M:$M,B27)*18+INDEX('Balance PLANTA'!$N:$N,B27)*17+INDEX('Balance PLANTA'!$O:$O,B27)*17,0)</f>
@@ -10020,7 +10013,7 @@
       </c>
       <c r="H28" s="0" t="n">
         <f aca="false">H27+G28</f>
-        <v>37004</v>
+        <v>30354</v>
       </c>
       <c r="I28" s="0" t="n">
         <f aca="false">IFERROR(INDEX('Balance PLANTA'!$L:$L,B28)*15+INDEX('Balance PLANTA'!$M:$M,B28)*18+INDEX('Balance PLANTA'!$N:$N,B28)*17+INDEX('Balance PLANTA'!$O:$O,B28)*17,0)</f>
@@ -10169,7 +10162,7 @@
       </c>
       <c r="H29" s="0" t="n">
         <f aca="false">H28+G29</f>
-        <v>37004</v>
+        <v>30354</v>
       </c>
       <c r="I29" s="0" t="n">
         <f aca="false">IFERROR(INDEX('Balance PLANTA'!$L:$L,B29)*15+INDEX('Balance PLANTA'!$M:$M,B29)*18+INDEX('Balance PLANTA'!$N:$N,B29)*17+INDEX('Balance PLANTA'!$O:$O,B29)*17,0)</f>
@@ -10318,7 +10311,7 @@
       </c>
       <c r="H30" s="0" t="n">
         <f aca="false">H29+G30</f>
-        <v>37004</v>
+        <v>30354</v>
       </c>
       <c r="I30" s="0" t="n">
         <f aca="false">IFERROR(INDEX('Balance PLANTA'!$L:$L,B30)*15+INDEX('Balance PLANTA'!$M:$M,B30)*18+INDEX('Balance PLANTA'!$N:$N,B30)*17+INDEX('Balance PLANTA'!$O:$O,B30)*17,0)</f>
@@ -10467,7 +10460,7 @@
       </c>
       <c r="H31" s="0" t="n">
         <f aca="false">H30+G31</f>
-        <v>37004</v>
+        <v>30354</v>
       </c>
       <c r="I31" s="0" t="n">
         <f aca="false">IFERROR(INDEX('Balance PLANTA'!$L:$L,B31)*15+INDEX('Balance PLANTA'!$M:$M,B31)*18+INDEX('Balance PLANTA'!$N:$N,B31)*17+INDEX('Balance PLANTA'!$O:$O,B31)*17,0)</f>
@@ -10616,7 +10609,7 @@
       </c>
       <c r="H32" s="0" t="n">
         <f aca="false">H31+G32</f>
-        <v>37004</v>
+        <v>30354</v>
       </c>
       <c r="I32" s="0" t="n">
         <f aca="false">IFERROR(INDEX('Balance PLANTA'!$L:$L,B32)*15+INDEX('Balance PLANTA'!$M:$M,B32)*18+INDEX('Balance PLANTA'!$N:$N,B32)*17+INDEX('Balance PLANTA'!$O:$O,B32)*17,0)</f>
@@ -10765,7 +10758,7 @@
       </c>
       <c r="H33" s="0" t="n">
         <f aca="false">H32+G33</f>
-        <v>37004</v>
+        <v>30354</v>
       </c>
       <c r="I33" s="0" t="n">
         <f aca="false">IFERROR(INDEX('Balance PLANTA'!$L:$L,B33)*15+INDEX('Balance PLANTA'!$M:$M,B33)*18+INDEX('Balance PLANTA'!$N:$N,B33)*17+INDEX('Balance PLANTA'!$O:$O,B33)*17,0)</f>
@@ -10914,7 +10907,7 @@
       </c>
       <c r="H34" s="0" t="n">
         <f aca="false">H33+G34</f>
-        <v>37004</v>
+        <v>30354</v>
       </c>
       <c r="I34" s="0" t="n">
         <f aca="false">IFERROR(INDEX('Balance PLANTA'!$L:$L,B34)*15+INDEX('Balance PLANTA'!$M:$M,B34)*18+INDEX('Balance PLANTA'!$N:$N,B34)*17+INDEX('Balance PLANTA'!$O:$O,B34)*17,0)</f>
@@ -11063,7 +11056,7 @@
       </c>
       <c r="H35" s="0" t="n">
         <f aca="false">H34+G35</f>
-        <v>37004</v>
+        <v>30354</v>
       </c>
       <c r="I35" s="0" t="n">
         <f aca="false">IFERROR(INDEX('Balance PLANTA'!$L:$L,B35)*15+INDEX('Balance PLANTA'!$M:$M,B35)*18+INDEX('Balance PLANTA'!$N:$N,B35)*17+INDEX('Balance PLANTA'!$O:$O,B35)*17,0)</f>
@@ -11212,7 +11205,7 @@
       </c>
       <c r="H36" s="0" t="n">
         <f aca="false">H35+G36</f>
-        <v>37004</v>
+        <v>30354</v>
       </c>
       <c r="I36" s="0" t="n">
         <f aca="false">IFERROR(INDEX('Balance PLANTA'!$L:$L,B36)*15+INDEX('Balance PLANTA'!$M:$M,B36)*18+INDEX('Balance PLANTA'!$N:$N,B36)*17+INDEX('Balance PLANTA'!$O:$O,B36)*17,0)</f>
@@ -11361,7 +11354,7 @@
       </c>
       <c r="H37" s="0" t="n">
         <f aca="false">H36+G37</f>
-        <v>37004</v>
+        <v>30354</v>
       </c>
       <c r="I37" s="0" t="n">
         <f aca="false">IFERROR(INDEX('Balance PLANTA'!$L:$L,B37)*15+INDEX('Balance PLANTA'!$M:$M,B37)*18+INDEX('Balance PLANTA'!$N:$N,B37)*17+INDEX('Balance PLANTA'!$O:$O,B37)*17,0)</f>
@@ -11510,7 +11503,7 @@
       </c>
       <c r="H38" s="0" t="n">
         <f aca="false">H37+G38</f>
-        <v>37004</v>
+        <v>30354</v>
       </c>
       <c r="I38" s="0" t="n">
         <f aca="false">IFERROR(INDEX('Balance PLANTA'!$L:$L,B38)*15+INDEX('Balance PLANTA'!$M:$M,B38)*18+INDEX('Balance PLANTA'!$N:$N,B38)*17+INDEX('Balance PLANTA'!$O:$O,B38)*17,0)</f>
@@ -11659,7 +11652,7 @@
       </c>
       <c r="H39" s="0" t="n">
         <f aca="false">H38+G39</f>
-        <v>37004</v>
+        <v>30354</v>
       </c>
       <c r="I39" s="0" t="n">
         <f aca="false">IFERROR(INDEX('Balance PLANTA'!$L:$L,B39)*15+INDEX('Balance PLANTA'!$M:$M,B39)*18+INDEX('Balance PLANTA'!$N:$N,B39)*17+INDEX('Balance PLANTA'!$O:$O,B39)*17,0)</f>
@@ -11808,7 +11801,7 @@
       </c>
       <c r="H40" s="0" t="n">
         <f aca="false">H39+G40</f>
-        <v>37004</v>
+        <v>30354</v>
       </c>
       <c r="I40" s="0" t="n">
         <f aca="false">IFERROR(INDEX('Balance PLANTA'!$L:$L,B40)*15+INDEX('Balance PLANTA'!$M:$M,B40)*18+INDEX('Balance PLANTA'!$N:$N,B40)*17+INDEX('Balance PLANTA'!$O:$O,B40)*17,0)</f>
@@ -11957,7 +11950,7 @@
       </c>
       <c r="H41" s="0" t="n">
         <f aca="false">H40+G41</f>
-        <v>37004</v>
+        <v>30354</v>
       </c>
       <c r="I41" s="0" t="n">
         <f aca="false">IFERROR(INDEX('Balance PLANTA'!$L:$L,B41)*15+INDEX('Balance PLANTA'!$M:$M,B41)*18+INDEX('Balance PLANTA'!$N:$N,B41)*17+INDEX('Balance PLANTA'!$O:$O,B41)*17,0)</f>
@@ -12963,7 +12956,7 @@
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AP68" s="0" t="str">
         <f aca="false">IF($R$13&lt;=0,"",FIFO_helper!$C$13)</f>
-        <v>20/07</v>
+        <v>21/07</v>
       </c>
       <c r="AQ68" s="0" t="str">
         <f aca="false">IF($R$13&lt;=0,"",$S$13)</f>
@@ -13099,7 +13092,7 @@
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AP72" s="0" t="str">
         <f aca="false">IF($AN$13&lt;=0,"",FIFO_helper!$C$13)</f>
-        <v>20/07</v>
+        <v>21/07</v>
       </c>
       <c r="AQ72" s="0" t="str">
         <f aca="false">IF($AN$13&lt;=0,"","(queda en planta)")</f>
@@ -13133,7 +13126,7 @@
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AP73" s="0" t="str">
         <f aca="false">IF($E$13&lt;=0,"",FIFO_helper!$C$13)</f>
-        <v>20/07</v>
+        <v>21/07</v>
       </c>
       <c r="AQ73" s="0" t="str">
         <f aca="false">IF($E$13&lt;=0,"","↳ Chancho (prod.)")</f>
@@ -13303,35 +13296,35 @@
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AP78" s="0" t="str">
         <f aca="false">IF($AN$14&lt;=0,"",FIFO_helper!$C$14)</f>
-        <v>21/07</v>
+        <v/>
       </c>
       <c r="AQ78" s="0" t="str">
         <f aca="false">IF($AN$14&lt;=0,"","(queda en planta)")</f>
-        <v>(queda en planta)</v>
+        <v/>
       </c>
       <c r="AR78" s="0" t="str">
         <f aca="false">IF($AN$14&lt;=0,"","PRIMERA")</f>
-        <v>PRIMERA</v>
+        <v/>
       </c>
       <c r="AS78" s="0" t="str">
         <f aca="false">""</f>
         <v/>
       </c>
-      <c r="AT78" s="0" t="n">
+      <c r="AT78" s="0" t="str">
         <f aca="false">IF($AN$14&lt;=0,"",$AN$14)</f>
-        <v>6650</v>
+        <v/>
       </c>
       <c r="AU78" s="0" t="str">
         <f aca="false">IF($AN$14&lt;=0,"","kg")</f>
-        <v>kg</v>
+        <v/>
       </c>
       <c r="AV78" s="0" t="n">
         <f aca="false">IF($AN$14&lt;=0,0,1)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW78" s="0" t="n">
         <f aca="false">AW77+AV78</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13365,7 +13358,7 @@
       </c>
       <c r="AW79" s="0" t="n">
         <f aca="false">AW78+AV79</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13399,7 +13392,7 @@
       </c>
       <c r="AW80" s="0" t="n">
         <f aca="false">AW79+AV80</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13433,7 +13426,7 @@
       </c>
       <c r="AW81" s="0" t="n">
         <f aca="false">AW80+AV81</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13467,7 +13460,7 @@
       </c>
       <c r="AW82" s="0" t="n">
         <f aca="false">AW81+AV82</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13501,7 +13494,7 @@
       </c>
       <c r="AW83" s="0" t="n">
         <f aca="false">AW82+AV83</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13535,7 +13528,7 @@
       </c>
       <c r="AW84" s="0" t="n">
         <f aca="false">AW83+AV84</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13569,7 +13562,7 @@
       </c>
       <c r="AW85" s="0" t="n">
         <f aca="false">AW84+AV85</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13603,7 +13596,7 @@
       </c>
       <c r="AW86" s="0" t="n">
         <f aca="false">AW85+AV86</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13637,7 +13630,7 @@
       </c>
       <c r="AW87" s="0" t="n">
         <f aca="false">AW86+AV87</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13671,7 +13664,7 @@
       </c>
       <c r="AW88" s="0" t="n">
         <f aca="false">AW87+AV88</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13705,7 +13698,7 @@
       </c>
       <c r="AW89" s="0" t="n">
         <f aca="false">AW88+AV89</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13739,7 +13732,7 @@
       </c>
       <c r="AW90" s="0" t="n">
         <f aca="false">AW89+AV90</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13773,7 +13766,7 @@
       </c>
       <c r="AW91" s="0" t="n">
         <f aca="false">AW90+AV91</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13807,7 +13800,7 @@
       </c>
       <c r="AW92" s="0" t="n">
         <f aca="false">AW91+AV92</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13841,7 +13834,7 @@
       </c>
       <c r="AW93" s="0" t="n">
         <f aca="false">AW92+AV93</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13875,7 +13868,7 @@
       </c>
       <c r="AW94" s="0" t="n">
         <f aca="false">AW93+AV94</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13909,7 +13902,7 @@
       </c>
       <c r="AW95" s="0" t="n">
         <f aca="false">AW94+AV95</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13943,7 +13936,7 @@
       </c>
       <c r="AW96" s="0" t="n">
         <f aca="false">AW95+AV96</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13977,7 +13970,7 @@
       </c>
       <c r="AW97" s="0" t="n">
         <f aca="false">AW96+AV97</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14011,7 +14004,7 @@
       </c>
       <c r="AW98" s="0" t="n">
         <f aca="false">AW97+AV98</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14045,7 +14038,7 @@
       </c>
       <c r="AW99" s="0" t="n">
         <f aca="false">AW98+AV99</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14079,7 +14072,7 @@
       </c>
       <c r="AW100" s="0" t="n">
         <f aca="false">AW99+AV100</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14113,7 +14106,7 @@
       </c>
       <c r="AW101" s="0" t="n">
         <f aca="false">AW100+AV101</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14147,7 +14140,7 @@
       </c>
       <c r="AW102" s="0" t="n">
         <f aca="false">AW101+AV102</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14181,7 +14174,7 @@
       </c>
       <c r="AW103" s="0" t="n">
         <f aca="false">AW102+AV103</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14215,7 +14208,7 @@
       </c>
       <c r="AW104" s="0" t="n">
         <f aca="false">AW103+AV104</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14249,7 +14242,7 @@
       </c>
       <c r="AW105" s="0" t="n">
         <f aca="false">AW104+AV105</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14283,7 +14276,7 @@
       </c>
       <c r="AW106" s="0" t="n">
         <f aca="false">AW105+AV106</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14317,7 +14310,7 @@
       </c>
       <c r="AW107" s="0" t="n">
         <f aca="false">AW106+AV107</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14351,7 +14344,7 @@
       </c>
       <c r="AW108" s="0" t="n">
         <f aca="false">AW107+AV108</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14385,7 +14378,7 @@
       </c>
       <c r="AW109" s="0" t="n">
         <f aca="false">AW108+AV109</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14419,7 +14412,7 @@
       </c>
       <c r="AW110" s="0" t="n">
         <f aca="false">AW109+AV110</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14453,7 +14446,7 @@
       </c>
       <c r="AW111" s="0" t="n">
         <f aca="false">AW110+AV111</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14487,7 +14480,7 @@
       </c>
       <c r="AW112" s="0" t="n">
         <f aca="false">AW111+AV112</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14521,7 +14514,7 @@
       </c>
       <c r="AW113" s="0" t="n">
         <f aca="false">AW112+AV113</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14555,7 +14548,7 @@
       </c>
       <c r="AW114" s="0" t="n">
         <f aca="false">AW113+AV114</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14589,7 +14582,7 @@
       </c>
       <c r="AW115" s="0" t="n">
         <f aca="false">AW114+AV115</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14623,7 +14616,7 @@
       </c>
       <c r="AW116" s="0" t="n">
         <f aca="false">AW115+AV116</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14657,7 +14650,7 @@
       </c>
       <c r="AW117" s="0" t="n">
         <f aca="false">AW116+AV117</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14691,7 +14684,7 @@
       </c>
       <c r="AW118" s="0" t="n">
         <f aca="false">AW117+AV118</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14725,7 +14718,7 @@
       </c>
       <c r="AW119" s="0" t="n">
         <f aca="false">AW118+AV119</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14759,7 +14752,7 @@
       </c>
       <c r="AW120" s="0" t="n">
         <f aca="false">AW119+AV120</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14793,7 +14786,7 @@
       </c>
       <c r="AW121" s="0" t="n">
         <f aca="false">AW120+AV121</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14827,7 +14820,7 @@
       </c>
       <c r="AW122" s="0" t="n">
         <f aca="false">AW121+AV122</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14861,7 +14854,7 @@
       </c>
       <c r="AW123" s="0" t="n">
         <f aca="false">AW122+AV123</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14895,7 +14888,7 @@
       </c>
       <c r="AW124" s="0" t="n">
         <f aca="false">AW123+AV124</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14929,7 +14922,7 @@
       </c>
       <c r="AW125" s="0" t="n">
         <f aca="false">AW124+AV125</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14963,7 +14956,7 @@
       </c>
       <c r="AW126" s="0" t="n">
         <f aca="false">AW125+AV126</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14997,7 +14990,7 @@
       </c>
       <c r="AW127" s="0" t="n">
         <f aca="false">AW126+AV127</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15031,7 +15024,7 @@
       </c>
       <c r="AW128" s="0" t="n">
         <f aca="false">AW127+AV128</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15065,7 +15058,7 @@
       </c>
       <c r="AW129" s="0" t="n">
         <f aca="false">AW128+AV129</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15099,7 +15092,7 @@
       </c>
       <c r="AW130" s="0" t="n">
         <f aca="false">AW129+AV130</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15133,7 +15126,7 @@
       </c>
       <c r="AW131" s="0" t="n">
         <f aca="false">AW130+AV131</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15167,7 +15160,7 @@
       </c>
       <c r="AW132" s="0" t="n">
         <f aca="false">AW131+AV132</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15201,7 +15194,7 @@
       </c>
       <c r="AW133" s="0" t="n">
         <f aca="false">AW132+AV133</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15235,7 +15228,7 @@
       </c>
       <c r="AW134" s="0" t="n">
         <f aca="false">AW133+AV134</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15269,7 +15262,7 @@
       </c>
       <c r="AW135" s="0" t="n">
         <f aca="false">AW134+AV135</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15303,7 +15296,7 @@
       </c>
       <c r="AW136" s="0" t="n">
         <f aca="false">AW135+AV136</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15337,7 +15330,7 @@
       </c>
       <c r="AW137" s="0" t="n">
         <f aca="false">AW136+AV137</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15371,7 +15364,7 @@
       </c>
       <c r="AW138" s="0" t="n">
         <f aca="false">AW137+AV138</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15405,7 +15398,7 @@
       </c>
       <c r="AW139" s="0" t="n">
         <f aca="false">AW138+AV139</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15439,7 +15432,7 @@
       </c>
       <c r="AW140" s="0" t="n">
         <f aca="false">AW139+AV140</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15473,7 +15466,7 @@
       </c>
       <c r="AW141" s="0" t="n">
         <f aca="false">AW140+AV141</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15507,7 +15500,7 @@
       </c>
       <c r="AW142" s="0" t="n">
         <f aca="false">AW141+AV142</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15541,7 +15534,7 @@
       </c>
       <c r="AW143" s="0" t="n">
         <f aca="false">AW142+AV143</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15575,7 +15568,7 @@
       </c>
       <c r="AW144" s="0" t="n">
         <f aca="false">AW143+AV144</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15609,7 +15602,7 @@
       </c>
       <c r="AW145" s="0" t="n">
         <f aca="false">AW144+AV145</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15643,7 +15636,7 @@
       </c>
       <c r="AW146" s="0" t="n">
         <f aca="false">AW145+AV146</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15677,7 +15670,7 @@
       </c>
       <c r="AW147" s="0" t="n">
         <f aca="false">AW146+AV147</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15711,7 +15704,7 @@
       </c>
       <c r="AW148" s="0" t="n">
         <f aca="false">AW147+AV148</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15745,7 +15738,7 @@
       </c>
       <c r="AW149" s="0" t="n">
         <f aca="false">AW148+AV149</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15779,7 +15772,7 @@
       </c>
       <c r="AW150" s="0" t="n">
         <f aca="false">AW149+AV150</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15813,7 +15806,7 @@
       </c>
       <c r="AW151" s="0" t="n">
         <f aca="false">AW150+AV151</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15847,7 +15840,7 @@
       </c>
       <c r="AW152" s="0" t="n">
         <f aca="false">AW151+AV152</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15881,7 +15874,7 @@
       </c>
       <c r="AW153" s="0" t="n">
         <f aca="false">AW152+AV153</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15915,7 +15908,7 @@
       </c>
       <c r="AW154" s="0" t="n">
         <f aca="false">AW153+AV154</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15949,7 +15942,7 @@
       </c>
       <c r="AW155" s="0" t="n">
         <f aca="false">AW154+AV155</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15983,7 +15976,7 @@
       </c>
       <c r="AW156" s="0" t="n">
         <f aca="false">AW155+AV156</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16017,7 +16010,7 @@
       </c>
       <c r="AW157" s="0" t="n">
         <f aca="false">AW156+AV157</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16051,7 +16044,7 @@
       </c>
       <c r="AW158" s="0" t="n">
         <f aca="false">AW157+AV158</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16085,7 +16078,7 @@
       </c>
       <c r="AW159" s="0" t="n">
         <f aca="false">AW158+AV159</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16119,7 +16112,7 @@
       </c>
       <c r="AW160" s="0" t="n">
         <f aca="false">AW159+AV160</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16153,7 +16146,7 @@
       </c>
       <c r="AW161" s="0" t="n">
         <f aca="false">AW160+AV161</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16187,7 +16180,7 @@
       </c>
       <c r="AW162" s="0" t="n">
         <f aca="false">AW161+AV162</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16221,7 +16214,7 @@
       </c>
       <c r="AW163" s="0" t="n">
         <f aca="false">AW162+AV163</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16255,7 +16248,7 @@
       </c>
       <c r="AW164" s="0" t="n">
         <f aca="false">AW163+AV164</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16289,7 +16282,7 @@
       </c>
       <c r="AW165" s="0" t="n">
         <f aca="false">AW164+AV165</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16323,7 +16316,7 @@
       </c>
       <c r="AW166" s="0" t="n">
         <f aca="false">AW165+AV166</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16357,7 +16350,7 @@
       </c>
       <c r="AW167" s="0" t="n">
         <f aca="false">AW166+AV167</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16391,7 +16384,7 @@
       </c>
       <c r="AW168" s="0" t="n">
         <f aca="false">AW167+AV168</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16425,7 +16418,7 @@
       </c>
       <c r="AW169" s="0" t="n">
         <f aca="false">AW168+AV169</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16459,7 +16452,7 @@
       </c>
       <c r="AW170" s="0" t="n">
         <f aca="false">AW169+AV170</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16493,7 +16486,7 @@
       </c>
       <c r="AW171" s="0" t="n">
         <f aca="false">AW170+AV171</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16527,7 +16520,7 @@
       </c>
       <c r="AW172" s="0" t="n">
         <f aca="false">AW171+AV172</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16561,7 +16554,7 @@
       </c>
       <c r="AW173" s="0" t="n">
         <f aca="false">AW172+AV173</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16595,7 +16588,7 @@
       </c>
       <c r="AW174" s="0" t="n">
         <f aca="false">AW173+AV174</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16629,7 +16622,7 @@
       </c>
       <c r="AW175" s="0" t="n">
         <f aca="false">AW174+AV175</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16663,7 +16656,7 @@
       </c>
       <c r="AW176" s="0" t="n">
         <f aca="false">AW175+AV176</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16697,7 +16690,7 @@
       </c>
       <c r="AW177" s="0" t="n">
         <f aca="false">AW176+AV177</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16731,7 +16724,7 @@
       </c>
       <c r="AW178" s="0" t="n">
         <f aca="false">AW177+AV178</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16765,7 +16758,7 @@
       </c>
       <c r="AW179" s="0" t="n">
         <f aca="false">AW178+AV179</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16799,7 +16792,7 @@
       </c>
       <c r="AW180" s="0" t="n">
         <f aca="false">AW179+AV180</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16833,7 +16826,7 @@
       </c>
       <c r="AW181" s="0" t="n">
         <f aca="false">AW180+AV181</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16867,7 +16860,7 @@
       </c>
       <c r="AW182" s="0" t="n">
         <f aca="false">AW181+AV182</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16901,7 +16894,7 @@
       </c>
       <c r="AW183" s="0" t="n">
         <f aca="false">AW182+AV183</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16935,7 +16928,7 @@
       </c>
       <c r="AW184" s="0" t="n">
         <f aca="false">AW183+AV184</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16969,7 +16962,7 @@
       </c>
       <c r="AW185" s="0" t="n">
         <f aca="false">AW184+AV185</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17003,7 +16996,7 @@
       </c>
       <c r="AW186" s="0" t="n">
         <f aca="false">AW185+AV186</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17037,7 +17030,7 @@
       </c>
       <c r="AW187" s="0" t="n">
         <f aca="false">AW186+AV187</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17071,7 +17064,7 @@
       </c>
       <c r="AW188" s="0" t="n">
         <f aca="false">AW187+AV188</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17105,7 +17098,7 @@
       </c>
       <c r="AW189" s="0" t="n">
         <f aca="false">AW188+AV189</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17139,7 +17132,7 @@
       </c>
       <c r="AW190" s="0" t="n">
         <f aca="false">AW189+AV190</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17173,7 +17166,7 @@
       </c>
       <c r="AW191" s="0" t="n">
         <f aca="false">AW190+AV191</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17207,7 +17200,7 @@
       </c>
       <c r="AW192" s="0" t="n">
         <f aca="false">AW191+AV192</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17241,7 +17234,7 @@
       </c>
       <c r="AW193" s="0" t="n">
         <f aca="false">AW192+AV193</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17275,7 +17268,7 @@
       </c>
       <c r="AW194" s="0" t="n">
         <f aca="false">AW193+AV194</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17309,7 +17302,7 @@
       </c>
       <c r="AW195" s="0" t="n">
         <f aca="false">AW194+AV195</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17343,7 +17336,7 @@
       </c>
       <c r="AW196" s="0" t="n">
         <f aca="false">AW195+AV196</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17377,7 +17370,7 @@
       </c>
       <c r="AW197" s="0" t="n">
         <f aca="false">AW196+AV197</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17411,7 +17404,7 @@
       </c>
       <c r="AW198" s="0" t="n">
         <f aca="false">AW197+AV198</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17445,7 +17438,7 @@
       </c>
       <c r="AW199" s="0" t="n">
         <f aca="false">AW198+AV199</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17479,7 +17472,7 @@
       </c>
       <c r="AW200" s="0" t="n">
         <f aca="false">AW199+AV200</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17513,7 +17506,7 @@
       </c>
       <c r="AW201" s="0" t="n">
         <f aca="false">AW200+AV201</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17547,7 +17540,7 @@
       </c>
       <c r="AW202" s="0" t="n">
         <f aca="false">AW201+AV202</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17581,7 +17574,7 @@
       </c>
       <c r="AW203" s="0" t="n">
         <f aca="false">AW202+AV203</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17615,7 +17608,7 @@
       </c>
       <c r="AW204" s="0" t="n">
         <f aca="false">AW203+AV204</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17649,7 +17642,7 @@
       </c>
       <c r="AW205" s="0" t="n">
         <f aca="false">AW204+AV205</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17683,7 +17676,7 @@
       </c>
       <c r="AW206" s="0" t="n">
         <f aca="false">AW205+AV206</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17717,7 +17710,7 @@
       </c>
       <c r="AW207" s="0" t="n">
         <f aca="false">AW206+AV207</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17751,7 +17744,7 @@
       </c>
       <c r="AW208" s="0" t="n">
         <f aca="false">AW207+AV208</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17785,7 +17778,7 @@
       </c>
       <c r="AW209" s="0" t="n">
         <f aca="false">AW208+AV209</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17819,7 +17812,7 @@
       </c>
       <c r="AW210" s="0" t="n">
         <f aca="false">AW209+AV210</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17853,7 +17846,7 @@
       </c>
       <c r="AW211" s="0" t="n">
         <f aca="false">AW210+AV211</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="212" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17887,7 +17880,7 @@
       </c>
       <c r="AW212" s="0" t="n">
         <f aca="false">AW211+AV212</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17921,7 +17914,7 @@
       </c>
       <c r="AW213" s="0" t="n">
         <f aca="false">AW212+AV213</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17955,7 +17948,7 @@
       </c>
       <c r="AW214" s="0" t="n">
         <f aca="false">AW213+AV214</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="215" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17989,7 +17982,7 @@
       </c>
       <c r="AW215" s="0" t="n">
         <f aca="false">AW214+AV215</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="216" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18023,7 +18016,7 @@
       </c>
       <c r="AW216" s="0" t="n">
         <f aca="false">AW215+AV216</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18057,7 +18050,7 @@
       </c>
       <c r="AW217" s="0" t="n">
         <f aca="false">AW216+AV217</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="218" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18091,7 +18084,7 @@
       </c>
       <c r="AW218" s="0" t="n">
         <f aca="false">AW217+AV218</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="219" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18125,7 +18118,7 @@
       </c>
       <c r="AW219" s="0" t="n">
         <f aca="false">AW218+AV219</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="220" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18159,7 +18152,7 @@
       </c>
       <c r="AW220" s="0" t="n">
         <f aca="false">AW219+AV220</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18193,7 +18186,7 @@
       </c>
       <c r="AW221" s="0" t="n">
         <f aca="false">AW220+AV221</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="222" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18227,7 +18220,7 @@
       </c>
       <c r="AW222" s="0" t="n">
         <f aca="false">AW221+AV222</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="223" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18261,7 +18254,7 @@
       </c>
       <c r="AW223" s="0" t="n">
         <f aca="false">AW222+AV223</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="224" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18295,7 +18288,7 @@
       </c>
       <c r="AW224" s="0" t="n">
         <f aca="false">AW223+AV224</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="225" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18329,7 +18322,7 @@
       </c>
       <c r="AW225" s="0" t="n">
         <f aca="false">AW224+AV225</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18363,7 +18356,7 @@
       </c>
       <c r="AW226" s="0" t="n">
         <f aca="false">AW225+AV226</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="227" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18397,7 +18390,7 @@
       </c>
       <c r="AW227" s="0" t="n">
         <f aca="false">AW226+AV227</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18431,7 +18424,7 @@
       </c>
       <c r="AW228" s="0" t="n">
         <f aca="false">AW227+AV228</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="229" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18465,7 +18458,7 @@
       </c>
       <c r="AW229" s="0" t="n">
         <f aca="false">AW228+AV229</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="230" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18499,7 +18492,7 @@
       </c>
       <c r="AW230" s="0" t="n">
         <f aca="false">AW229+AV230</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="231" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18533,7 +18526,7 @@
       </c>
       <c r="AW231" s="0" t="n">
         <f aca="false">AW230+AV231</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="232" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18567,7 +18560,7 @@
       </c>
       <c r="AW232" s="0" t="n">
         <f aca="false">AW231+AV232</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="233" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18601,7 +18594,7 @@
       </c>
       <c r="AW233" s="0" t="n">
         <f aca="false">AW232+AV233</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="234" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18635,7 +18628,7 @@
       </c>
       <c r="AW234" s="0" t="n">
         <f aca="false">AW233+AV234</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="235" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18669,7 +18662,7 @@
       </c>
       <c r="AW235" s="0" t="n">
         <f aca="false">AW234+AV235</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="236" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18703,7 +18696,7 @@
       </c>
       <c r="AW236" s="0" t="n">
         <f aca="false">AW235+AV236</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="237" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18737,7 +18730,7 @@
       </c>
       <c r="AW237" s="0" t="n">
         <f aca="false">AW236+AV237</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="238" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18771,7 +18764,7 @@
       </c>
       <c r="AW238" s="0" t="n">
         <f aca="false">AW237+AV238</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="239" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18805,7 +18798,7 @@
       </c>
       <c r="AW239" s="0" t="n">
         <f aca="false">AW238+AV239</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="240" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18839,7 +18832,7 @@
       </c>
       <c r="AW240" s="0" t="n">
         <f aca="false">AW239+AV240</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="241" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18873,7 +18866,7 @@
       </c>
       <c r="AW241" s="0" t="n">
         <f aca="false">AW240+AV241</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
